--- a/Constrained_BO/results/final_charging_opt_results/RW12/comparison_table.xlsx
+++ b/Constrained_BO/results/final_charging_opt_results/RW12/comparison_table.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -528,7 +528,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>
@@ -540,32 +540,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CC 1C</t>
+          <t>CCCV 1C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.93</v>
+        <v>27.33</v>
       </c>
       <c r="D3" t="n">
         <v>40.02</v>
       </c>
       <c r="E3" t="n">
-        <v>21.52</v>
+        <v>21.5</v>
       </c>
       <c r="F3" t="n">
-        <v>78.48</v>
+        <v>78.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.52</v>
+        <v>-1.5</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.18</v>
+        <v>-7.25</v>
       </c>
       <c r="I3" t="n">
-        <v>53.15</v>
+        <v>41.62</v>
       </c>
       <c r="J3" t="n">
-        <v>24.96</v>
+        <v>24.49</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -577,7 +577,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>
@@ -589,32 +589,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CC 2C</t>
+          <t>CCCV 2C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.95</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
         <v>40.01</v>
       </c>
       <c r="E4" t="n">
-        <v>21.62</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>78.38</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.62</v>
+        <v>-1</v>
       </c>
       <c r="H4" t="n">
-        <v>-6.8</v>
+        <v>-4.38</v>
       </c>
       <c r="I4" t="n">
-        <v>76.61</v>
+        <v>61.55</v>
       </c>
       <c r="J4" t="n">
-        <v>30.6</v>
+        <v>25</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>

--- a/Constrained_BO/results/final_charging_opt_results/RW12/comparison_table.xlsx
+++ b/Constrained_BO/results/final_charging_opt_results/RW12/comparison_table.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,32 +589,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CCCV 2C</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>29.75</v>
       </c>
       <c r="D4" t="n">
-        <v>40.01</v>
+        <v>40.02</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>20.96</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.38</v>
+        <v>-4.58</v>
       </c>
       <c r="I4" t="n">
-        <v>61.55</v>
+        <v>36.45</v>
       </c>
       <c r="J4" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>GP-BO</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -687,32 +687,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GP-BO</t>
+          <t>GP-BO (min Q)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.75</v>
+        <v>86.63</v>
       </c>
       <c r="D6" t="n">
-        <v>40.02</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>20.96</v>
+        <v>19.46</v>
       </c>
       <c r="F6" t="n">
-        <v>79.04000000000001</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.96</v>
+        <v>0.54</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.58</v>
+        <v>2.8</v>
       </c>
       <c r="I6" t="n">
-        <v>36.45</v>
+        <v>-85.05</v>
       </c>
       <c r="J6" t="n">
-        <v>24.2</v>
+        <v>24.08</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -723,55 +723,6 @@
         </is>
       </c>
       <c r="M6" t="inlineStr">
-        <is>
-          <t>CCCV ½C</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RW12</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GP-BO (min Q)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>86.63</v>
-      </c>
-      <c r="D7" t="n">
-        <v>40</v>
-      </c>
-      <c r="E7" t="n">
-        <v>19.46</v>
-      </c>
-      <c r="F7" t="n">
-        <v>80.54000000000001</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-85.05</v>
-      </c>
-      <c r="J7" t="n">
-        <v>24.08</v>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
         <is>
           <t>CCCV ½C</t>
         </is>
